--- a/data/trans_orig/IP2004-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120026</t>
+          <t>119910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127117</t>
+          <t>127143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133118</t>
+          <t>133007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140558</t>
+          <t>140107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255754</t>
+          <t>257075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266073</t>
+          <t>266362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12707</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172141</t>
+          <t>172673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181320</t>
+          <t>181189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190842</t>
+          <t>190832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199542</t>
+          <t>199546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365790</t>
+          <t>366790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>378781</t>
+          <t>378776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121387</t>
+          <t>120880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128288</t>
+          <t>128309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128436</t>
+          <t>128784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135244</t>
+          <t>135181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>252607</t>
+          <t>251617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261830</t>
+          <t>262207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188580</t>
+          <t>189113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196569</t>
+          <t>196628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187374</t>
+          <t>187731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195403</t>
+          <t>195181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380200</t>
+          <t>380192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390530</t>
+          <t>390428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>55184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612709</t>
+          <t>613056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>627687</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>651244</t>
+          <t>650906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665655</t>
+          <t>665422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268872</t>
+          <t>1268682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1289541</t>
+          <t>1288971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123946</t>
+          <t>123445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131584</t>
+          <t>131163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130007</t>
+          <t>129825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139246</t>
+          <t>139118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257071</t>
+          <t>258231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269096</t>
+          <t>269760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>181491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188405</t>
+          <t>188400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203920</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210156</t>
+          <t>210179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>387946</t>
+          <t>388117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>397425</t>
+          <t>397397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>137217</t>
+          <t>137595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143973</t>
+          <t>143978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145629</t>
+          <t>145183</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151686</t>
+          <t>151680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284912</t>
+          <t>285822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>294201</t>
+          <t>294543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178399</t>
+          <t>178665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188982</t>
+          <t>189293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186057</t>
+          <t>186686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194386</t>
+          <t>194383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369378</t>
+          <t>370175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>382025</t>
+          <t>382064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>632658</t>
+          <t>632625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>648288</t>
+          <t>647653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676389</t>
+          <t>676512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>691303</t>
+          <t>691510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1315377</t>
+          <t>1314724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336359</t>
+          <t>1336064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112885</t>
+          <t>113704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122593</t>
+          <t>122267</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130638</t>
+          <t>130382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137706</t>
+          <t>137700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247873</t>
+          <t>247216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258857</t>
+          <t>258522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185229</t>
+          <t>184934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191494</t>
+          <t>191513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203190</t>
+          <t>204175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209956</t>
+          <t>209967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391921</t>
+          <t>391681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400278</t>
+          <t>400244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140684</t>
+          <t>140142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146855</t>
+          <t>146632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155664</t>
+          <t>155331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159844</t>
+          <t>159846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298427</t>
+          <t>297781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>305913</t>
+          <t>306019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182671</t>
+          <t>183308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190798</t>
+          <t>190828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183441</t>
+          <t>183765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189963</t>
+          <t>189964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370314</t>
+          <t>369345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>379394</t>
+          <t>379222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>631885</t>
+          <t>631488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646158</t>
+          <t>646063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683572</t>
+          <t>682896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694288</t>
+          <t>694113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319294</t>
+          <t>1319161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337587</t>
+          <t>1336994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128351</t>
+          <t>128596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135931</t>
+          <t>135911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243830</t>
+          <t>243786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250923</t>
+          <t>250929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177129</t>
+          <t>176596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184677</t>
+          <t>184586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235730</t>
+          <t>235589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246015</t>
+          <t>246285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415683</t>
+          <t>416635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>429035</t>
+          <t>429011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>9577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>183618</t>
+          <t>183930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187621</t>
+          <t>187631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175427</t>
+          <t>175638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182549</t>
+          <t>182611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>362113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369531</t>
+          <t>369583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159694</t>
+          <t>159374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169555</t>
+          <t>169451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176744</t>
+          <t>176684</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332672</t>
+          <t>333865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342034</t>
+          <t>342046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,42 +7966,42 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>17057</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10765</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25750</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17057</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10934</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26191</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>641143</t>
+          <t>642691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>652100</t>
+          <t>652064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,47 +8074,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>730408</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>721715</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>736700</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>97,72%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>730408</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>721274</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>736531</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1368732</t>
+          <t>1367806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1386396</t>
+          <t>1387381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2004-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5195</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9333</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4502</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1863</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9096</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8571</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5195</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2803</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9903</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>137715</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>133577</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>140189</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>124504</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>119910</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>127143</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>120435</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>127115</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>137715</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>133007</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>140107</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257075</t>
+          <t>256577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266362</t>
+          <t>266513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142910</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142910</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>142910</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>142910</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>142910</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>142910</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7369</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12719</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8411</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13111</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13727</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7369</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12717</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>196180</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>190830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>199544</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>177373</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>172673</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181189</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>172057</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>180814</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>196180</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>190832</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>199546</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366790</t>
+          <t>365735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>378776</t>
+          <t>378818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>203549</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>203549</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>203549</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>203549</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>203549</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>203549</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8694</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4935</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1899</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9328</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4440</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8322</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132666</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>128412</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>135312</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>125273</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120880</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>128309</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>121087</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>127785</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>132666</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>128784</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>135181</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>252732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262207</t>
+          <t>261985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>137106</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>137106</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>137106</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>130208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>130208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>130208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>137106</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>137106</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>137106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4544</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8985</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4202</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9051</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9583</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9408</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>192595</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>188154</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>195563</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>193962</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>189113</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>196628</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>188581</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>196585</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>192595</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>187731</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>195181</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380192</t>
+          <t>380808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390428</t>
+          <t>390610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197139</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197139</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197139</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>198164</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>198164</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>198164</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>197139</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>197139</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>197139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,67 +2100,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15280</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29635</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>22051</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15021</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30106</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15223</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>30597</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15282</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29798</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>34429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55184</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>659156</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>651069</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>665424</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>621111</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>613056</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>628141</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>612565</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>627939</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>990</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>659156</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>650906</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>665422</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268682</t>
+          <t>1269538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1288971</t>
+          <t>1289437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>680704</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>680704</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>680704</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>960</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>643162</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>643162</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>643162</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>680704</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>680704</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>680704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6408</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12444</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4509</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9723</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9488</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6408</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3009</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12302</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>135719</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>129683</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>139383</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>128659</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>123445</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131163</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>123680</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131552</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>135719</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>129825</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>139118</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258231</t>
+          <t>257518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269760</t>
+          <t>269375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5095</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9353</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9458</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3695</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8090</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>207774</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>204148</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>210202</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>185749</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>181491</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>188400</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>181386</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>188262</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>207774</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>203379</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>210179</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>388117</t>
+          <t>387745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>397397</t>
+          <t>397319</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>211469</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>211469</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>211469</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>190844</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>190844</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>190844</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>211469</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>211469</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>211469</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2944</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7063</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7083</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7110</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149804</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145289</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151690</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>141714</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137595</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>143978</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>137575</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>143986</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,96%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149804</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>145183</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>151680</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285822</t>
+          <t>286036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>294543</t>
+          <t>294780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9488</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8407</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4254</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14882</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15118</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4527</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9580</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>191739</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>186778</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>194391</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>185140</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>178665</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>189293</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>178429</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>189006</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>191739</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>186686</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>194383</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370175</t>
+          <t>369311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>382064</t>
+          <t>381668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11243</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26097</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20955</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14564</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29592</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14641</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29159</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10646</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25644</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49648</t>
+          <t>49547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>685036</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>676059</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>690913</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>924</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>641262</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>632625</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>647653</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>633058</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>647576</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>685036</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>676512</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>691510</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1314724</t>
+          <t>1314825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336064</t>
+          <t>1335165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>702156</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>702156</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>702156</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>662217</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>662217</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>662217</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8013</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5883</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2402</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10965</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11775</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8728</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>135189</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>131097</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>137716</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>118786</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>113704</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>122267</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>112894</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>122468</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>135189</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>130382</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>137700</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247216</t>
+          <t>246226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258522</t>
+          <t>258383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6813</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4246</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8384</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8018</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2814</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6502</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>207863</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203864</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>209965</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>189072</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>184934</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>191513</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>185300</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191523</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,07%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>207863</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>204175</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>209967</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>610</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391681</t>
+          <t>392067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400244</t>
+          <t>400385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3777</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1535</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8025</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7518</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5096</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158518</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154958</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159841</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>144390</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140142</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>146632</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>140649</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>146892</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158518</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>155331</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>159846</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297781</t>
+          <t>298373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306019</t>
+          <t>305872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4686</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9175</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1668</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9397</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>187876</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>184037</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>189964</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>187797</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>183308</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>190828</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>183086</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>190815</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>187876</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>183765</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>189964</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369345</t>
+          <t>369940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>379222</t>
+          <t>379518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6984</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17556</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>18592</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12574</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27149</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12341</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>26686</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11449</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17999</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40371</t>
+          <t>39957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689446</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683339</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693911</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>961</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>640045</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>631488</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>646063</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>631951</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>646296</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,18%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>689446</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>682896</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>694113</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319161</t>
+          <t>1319575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336994</t>
+          <t>1338206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658637</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658637</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658637</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8019</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8161</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119885</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114860</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122087</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>119302</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>133465</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>128596</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>135911</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>350</t>
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>248535</t>
+          <t>239187</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243786</t>
+          <t>234418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250929</t>
+          <t>241433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5994</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11329</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10302</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>226562</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>221227</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>230026</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>181977</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>176596</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184586</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>242305</t>
+          <t>176446</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235589</t>
+          <t>170518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246285</t>
+          <t>179619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>424282</t>
+          <t>403008</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416635</t>
+          <t>396094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>429011</t>
+          <t>407808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3348</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8054</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1529</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3378</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163799</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159093</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166230</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>186458</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>183930</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>187631</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180325</t>
+          <t>153177</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175638</t>
+          <t>149841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182611</t>
+          <t>154317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>366783</t>
+          <t>316976</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>362113</t>
+          <t>311982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369583</t>
+          <t>319787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8161</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6742</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3550</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8412</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163317</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158447</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>165271</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>164916</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159374</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>163934</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>159086</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>165171</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,32%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174313</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>169451</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>176684</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>463</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>339229</t>
+          <t>327251</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333865</t>
+          <t>322198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342046</t>
+          <t>330003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10377</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23077</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7955</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>4007</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13380</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17057</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10765</t>
-        </is>
-      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23583</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>34073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>673563</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>666113</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>678813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>648420</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>642691</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>652064</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>730408</t>
+          <t>612859</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>721715</t>
+          <t>606225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736700</t>
+          <t>616807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1378829</t>
+          <t>1286421</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1367806</t>
+          <t>1275931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1387381</t>
+          <t>1294064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
